--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38470756-2153-422B-9F76-5A103C550C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0F4117-27CE-493B-B8ED-DD5A36412E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="115">
   <si>
     <t>type</t>
   </si>
@@ -243,9 +243,6 @@
   </si>
   <si>
     <t>assign</t>
-  </si>
-  <si>
-    <t>nome_formulario</t>
   </si>
   <si>
     <t>display.adate.fromYear</t>
@@ -543,11 +540,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -995,7 +992,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1011,7 +1008,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1019,7 +1016,7 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1027,7 +1024,7 @@
         <v>66</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1059,18 +1056,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
         <v>73</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s">
         <v>75</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1147,10 +1144,10 @@
         <v>26</v>
       </c>
       <c r="O1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="Q1" t="s">
         <v>27</v>
@@ -1236,7 +1233,7 @@
         <v>56</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -1261,13 +1258,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>57</v>
@@ -1288,34 +1285,34 @@
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
@@ -1420,21 +1417,21 @@
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
@@ -1567,7 +1564,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1578,7 +1575,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1619,101 +1616,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2218,7 +2215,7 @@
         <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2223,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2234,14 +2231,14 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2249,7 +2246,7 @@
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2257,15 +2254,15 @@
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2273,7 +2270,7 @@
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2281,7 +2278,7 @@
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2289,7 +2286,7 @@
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2298,15 +2295,15 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2311,7 @@
         <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2327,26 +2324,26 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2354,7 +2351,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2362,15 +2359,15 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>113</v>
+      <c r="B21" s="13" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2389,7 +2386,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2397,23 +2394,23 @@
         <v>5</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0F4117-27CE-493B-B8ED-DD5A36412E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15597B65-24D5-487B-843C-ADF68E9B6E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
   <si>
     <t>type</t>
   </si>
@@ -200,9 +200,6 @@
     <t>nota</t>
   </si>
   <si>
-    <t>febre</t>
-  </si>
-  <si>
     <t>tdr</t>
   </si>
   <si>
@@ -341,30 +338,6 @@
     <t>Leucocitos</t>
   </si>
   <si>
-    <t>data_consulta</t>
-  </si>
-  <si>
-    <t>gravidez</t>
-  </si>
-  <si>
-    <t>peso</t>
-  </si>
-  <si>
-    <t>procedencia</t>
-  </si>
-  <si>
-    <t>temperatura</t>
-  </si>
-  <si>
-    <t>diagnostico</t>
-  </si>
-  <si>
-    <t>diagno_secund</t>
-  </si>
-  <si>
-    <t>hospitaliza</t>
-  </si>
-  <si>
     <t>DOB_idade</t>
   </si>
   <si>
@@ -374,10 +347,10 @@
     <t>id_formssentinela</t>
   </si>
   <si>
-    <t>select_one_dropdown</t>
-  </si>
-  <si>
-    <t>comentario</t>
+    <t>display.deselect</t>
+  </si>
+  <si>
+    <t>select_one_integer</t>
   </si>
 </sst>
 </file>
@@ -992,7 +965,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1008,7 +981,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1016,12 +989,12 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>40</v>
@@ -1056,18 +1029,18 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
         <v>72</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" t="s">
         <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1078,7 +1051,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Z45"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -1094,13 +1067,13 @@
     <col min="11" max="11" width="17.875" style="5" customWidth="1"/>
     <col min="12" max="12" width="30" style="2" customWidth="1"/>
     <col min="13" max="13" width="10.75" style="2"/>
-    <col min="14" max="14" width="40.875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="19.875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="13.25" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="10.75" style="2"/>
+    <col min="14" max="15" width="40.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="19.875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13.25" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
@@ -1143,41 +1116,44 @@
       <c r="N1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>29</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>31</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>32</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>33</v>
-      </c>
-      <c r="X1" t="s">
-        <v>18</v>
       </c>
       <c r="Y1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
@@ -1199,14 +1175,15 @@
       <c r="W2"/>
       <c r="X2"/>
       <c r="Y2"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z2"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
         <v>49</v>
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1215,124 +1192,127 @@
         <v>54</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="3"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="L6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O6"/>
+      <c r="O6" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="P6"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q6"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P7"/>
+      <c r="Q7"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D8" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8"/>
+      <c r="Q8"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O7"/>
-      <c r="P7"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="O8"/>
-      <c r="P8"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="O9"/>
       <c r="P9"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Q9"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
@@ -1564,7 +1544,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1575,7 +1555,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1616,101 +1596,101 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2">
         <v>3</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2195,7 +2175,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.25" customWidth="1"/>
@@ -2212,238 +2192,150 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>52</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>110</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>62</v>
+      <c r="B10" s="13" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>104</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" t="s">
         <v>105</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>114</v>
-      </c>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>112</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\ODKX\app-designer\app\config\tables\resultado\forms\resultado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15597B65-24D5-487B-843C-ADF68E9B6E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E6FBEE-886E-45BF-B064-B732A6BE97B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -1270,6 +1270,9 @@
       <c r="G11" s="2" t="s">
         <v>96</v>
       </c>
+      <c r="L11" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
@@ -1282,6 +1285,9 @@
       <c r="G12" s="2" t="s">
         <v>100</v>
       </c>
+      <c r="L12" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
@@ -1293,6 +1299,9 @@
       </c>
       <c r="G13" s="2" t="s">
         <v>98</v>
+      </c>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E6FBEE-886E-45BF-B064-B732A6BE97B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE324C9E-0190-4B93-A503-052C9D1E5B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="107">
   <si>
     <t>type</t>
   </si>
@@ -323,9 +323,6 @@
     <t>GE</t>
   </si>
   <si>
-    <t>Gota espessa</t>
-  </si>
-  <si>
     <t>hb</t>
   </si>
   <si>
@@ -351,6 +348,12 @@
   </si>
   <si>
     <t>select_one_integer</t>
+  </si>
+  <si>
+    <t>data('GE')&lt;10000 || data('GE')==88888</t>
+  </si>
+  <si>
+    <t>Gota espessa: incontavel por (88888)</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1120,7 @@
         <v>26</v>
       </c>
       <c r="O1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>69</v>
@@ -1201,7 +1204,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>37</v>
@@ -1235,7 +1238,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>75</v>
@@ -1268,7 +1271,10 @@
         <v>95</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="L11" s="2" t="b">
         <v>1</v>
@@ -1280,10 +1286,10 @@
       </c>
       <c r="E12" s="10"/>
       <c r="F12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="L12" s="2" t="b">
         <v>1</v>
@@ -1295,10 +1301,10 @@
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="L13" s="2" t="b">
         <v>1</v>
@@ -1553,7 +1559,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
@@ -1564,7 +1570,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -2204,7 +2210,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2268,7 +2274,7 @@
         <v>45</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,7 +2282,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>55</v>
@@ -2284,7 +2290,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>92</v>
@@ -2303,7 +2309,7 @@
         <v>94</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2311,7 +2317,7 @@
         <v>94</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE324C9E-0190-4B93-A503-052C9D1E5B66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675DEA2B-5668-462E-908D-B17F86E04527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="prompt_types" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">survey!$D$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">survey!$D$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
   <si>
     <t>type</t>
   </si>
@@ -354,6 +354,15 @@
   </si>
   <si>
     <t>Gota espessa: incontavel por (88888)</t>
+  </si>
+  <si>
+    <t>campo</t>
+  </si>
+  <si>
+    <t>N campo</t>
+  </si>
+  <si>
+    <t>default</t>
   </si>
 </sst>
 </file>
@@ -486,7 +495,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -518,6 +527,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1054,7 +1066,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Z45"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -1064,19 +1076,20 @@
     <col min="5" max="5" width="16.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="15.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="63" style="2" customWidth="1"/>
-    <col min="8" max="8" width="26.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="35.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="35.125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="30" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.75" style="2"/>
-    <col min="14" max="15" width="40.875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="19.875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.25" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="10.75" style="2"/>
+    <col min="8" max="8" width="20" style="2" customWidth="1"/>
+    <col min="9" max="9" width="26.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="35.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="35.125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="17.875" style="5" customWidth="1"/>
+    <col min="13" max="13" width="30" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.75" style="2"/>
+    <col min="15" max="16" width="40.875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="19.875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.25" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>48</v>
       </c>
@@ -1098,70 +1111,73 @@
       <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>21</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>25</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>26</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>103</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>28</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>29</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>30</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>32</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>33</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>18</v>
       </c>
       <c r="Z1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="6"/>
-      <c r="I2"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="6"/>
       <c r="J2"/>
       <c r="K2"/>
       <c r="L2"/>
@@ -1179,14 +1195,15 @@
       <c r="X2"/>
       <c r="Y2"/>
       <c r="Z2"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA2"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B4" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="L4" s="4"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>51</v>
       </c>
@@ -1200,9 +1217,10 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="K5" s="1"/>
+      <c r="L5" s="3"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D6" s="2" t="s">
         <v>104</v>
       </c>
@@ -1215,28 +1233,28 @@
       <c r="G6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H6"/>
       <c r="I6"/>
-      <c r="L6" s="2" t="b">
+      <c r="J6"/>
+      <c r="M6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="O6" s="2" t="b">
+      <c r="P6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="P6"/>
       <c r="Q6"/>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R6"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P7"/>
       <c r="Q7"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D8" s="2" t="s">
         <v>104</v>
       </c>
@@ -1249,20 +1267,20 @@
       <c r="G8" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="P8"/>
       <c r="Q8"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R8"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="P9"/>
       <c r="Q9"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="R9"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D11" s="2" t="s">
         <v>5</v>
       </c>
@@ -1273,234 +1291,266 @@
       <c r="G11" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L11" s="2" t="b">
+      <c r="M11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D12" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" s="10"/>
+        <v>5</v>
+      </c>
+      <c r="E12" s="15"/>
       <c r="F12" s="2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L12" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="H12" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="L13" s="2" t="b">
+      <c r="M14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D16" s="2" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E17" s="10"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E18" s="10"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="K21" s="4"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H21" s="15"/>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="K22" s="4"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H22" s="15"/>
+      <c r="I22" s="10"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H23" s="15"/>
+      <c r="I23" s="10"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H24" s="15"/>
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="H25" s="15"/>
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="K29" s="4"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="10"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H26" s="15"/>
+      <c r="I26" s="10"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="10"/>
+    </row>
+    <row r="28" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L30" s="4"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="10"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="16"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="10"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="10"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="10"/>
       <c r="C40" s="10"/>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="15"/>
+      <c r="I40" s="10"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H41" s="15"/>
+      <c r="I41" s="10"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B42" s="10"/>
       <c r="C42" s="10"/>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H42" s="15"/>
+      <c r="I42" s="10"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H43" s="15"/>
+      <c r="I43" s="10"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="H44" s="15"/>
+      <c r="I44" s="10"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="10"/>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="D1:K1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:L1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675DEA2B-5668-462E-908D-B17F86E04527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DC824C-6DF0-459D-A8F1-0B418F3872D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
   <si>
     <t>type</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>default</t>
+  </si>
+  <si>
+    <t>"200"</t>
   </si>
 </sst>
 </file>
@@ -1309,8 +1312,8 @@
       <c r="G12" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H12" s="2">
-        <v>200</v>
+      <c r="H12" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DC824C-6DF0-459D-A8F1-0B418F3872D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6227BAD-EFC0-4A82-B26E-7601632A9EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -365,7 +365,7 @@
     <t>default</t>
   </si>
   <si>
-    <t>"200"</t>
+    <t>data('campo')==200</t>
   </si>
 </sst>
 </file>
@@ -991,7 +991,7 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>2022010601</v>
+        <v>2022022800</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6227BAD-EFC0-4A82-B26E-7601632A9EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0EA450-119D-49CF-8CB7-3E72C3E08017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
   <si>
     <t>type</t>
   </si>
@@ -353,19 +353,28 @@
     <t>data('GE')&lt;10000 || data('GE')==88888</t>
   </si>
   <si>
-    <t>Gota espessa: incontavel por (88888)</t>
-  </si>
-  <si>
     <t>campo</t>
   </si>
   <si>
-    <t>N campo</t>
-  </si>
-  <si>
     <t>default</t>
   </si>
   <si>
-    <t>data('campo')==200</t>
+    <t>Gota espessa: N/200 campo</t>
+  </si>
+  <si>
+    <t>N campo: Somente se o campo contado é menor que 200</t>
+  </si>
+  <si>
+    <t>ncampo</t>
+  </si>
+  <si>
+    <t>data('campo')=="" ? 200 : data('campo')</t>
+  </si>
+  <si>
+    <t>data('campo') &lt;200</t>
+  </si>
+  <si>
+    <t>Somente en caso que é menor que 200</t>
   </si>
 </sst>
 </file>
@@ -498,7 +507,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -530,6 +539,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1069,7 +1081,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -1115,7 +1127,7 @@
         <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>24</v>
@@ -1292,7 +1304,7 @@
         <v>95</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>105</v>
@@ -1302,93 +1314,90 @@
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="D13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" s="2" t="b">
-        <v>1</v>
+        <v>109</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="2" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M14" s="2" t="b">
+      <c r="M16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="D17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E18" s="10"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="10"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="10"/>
-      <c r="L22" s="4"/>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="E20" s="10"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="10"/>
@@ -1399,7 +1408,6 @@
       <c r="G23" s="10"/>
       <c r="H23" s="15"/>
       <c r="I23" s="10"/>
-      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="10"/>
@@ -1410,6 +1418,7 @@
       <c r="G24" s="10"/>
       <c r="H24" s="15"/>
       <c r="I24" s="10"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="10"/>
@@ -1420,6 +1429,7 @@
       <c r="G25" s="10"/>
       <c r="H25" s="15"/>
       <c r="I25" s="10"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="10"/>
@@ -1441,57 +1451,57 @@
       <c r="H27" s="15"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="L30" s="4"/>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="10"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="10"/>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="10"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="10"/>
+    </row>
+    <row r="30" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L32" s="4"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="16"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
       <c r="H39" s="15"/>
       <c r="I39" s="10"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="10"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
       <c r="H40" s="15"/>
       <c r="I40" s="10"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
       <c r="H41" s="15"/>
       <c r="I41" s="10"/>
     </row>
@@ -1545,15 +1555,35 @@
       <c r="H46" s="15"/>
       <c r="I46" s="10"/>
     </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="10"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="10"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:L1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0EA450-119D-49CF-8CB7-3E72C3E08017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E85394-6988-4F3C-9CCB-606FEF30227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="116">
   <si>
     <t>type</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>Somente en caso que é menor que 200</t>
+  </si>
+  <si>
+    <t>lab</t>
+  </si>
+  <si>
+    <t>Inicias de Laboratorista</t>
   </si>
 </sst>
 </file>
@@ -507,7 +513,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -539,6 +545,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1357,9 +1366,6 @@
       <c r="G15" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M15" s="2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D16" s="2" t="s">
@@ -1372,9 +1378,6 @@
       <c r="G16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M16" s="2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
@@ -1383,7 +1386,16 @@
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="E18" s="10"/>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
@@ -1486,22 +1498,22 @@
       <c r="I39" s="10"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
       <c r="H40" s="15"/>
       <c r="I40" s="10"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
       <c r="H41" s="15"/>
       <c r="I41" s="10"/>
     </row>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66E85394-6988-4F3C-9CCB-606FEF30227F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25843810-BF45-46F1-AD68-3C3C8A7947B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>22</v>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25843810-BF45-46F1-AD68-3C3C8A7947B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242E30FD-2617-4FEF-89ED-1DDAECDF04C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -1379,13 +1379,13 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
       <c r="E17" s="10"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D18" s="2" t="s">
         <v>45</v>
       </c>
@@ -1396,8 +1396,11 @@
       <c r="G18" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M18" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
         <v>4</v>
       </c>
@@ -1408,10 +1411,10 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
       <c r="E20" s="10"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
@@ -1421,7 +1424,7 @@
       <c r="H23" s="15"/>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
@@ -1432,7 +1435,7 @@
       <c r="I24" s="10"/>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
@@ -1443,7 +1446,7 @@
       <c r="I25" s="10"/>
       <c r="L25" s="4"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
       <c r="D26" s="10"/>
@@ -1453,7 +1456,7 @@
       <c r="H26" s="15"/>
       <c r="I26" s="10"/>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" s="10"/>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
@@ -1463,7 +1466,7 @@
       <c r="H27" s="15"/>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B28" s="10"/>
       <c r="C28" s="10"/>
       <c r="D28" s="10"/>
@@ -1473,7 +1476,7 @@
       <c r="H28" s="15"/>
       <c r="I28" s="10"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
@@ -1483,8 +1486,8 @@
       <c r="H29" s="15"/>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="2:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="L32" s="4"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242E30FD-2617-4FEF-89ED-1DDAECDF04C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD653C97-2294-439E-A1FF-EDA0E3BE3C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD653C97-2294-439E-A1FF-EDA0E3BE3C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50A180A-4271-4CF9-A8ED-0C36C4D34AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="119">
   <si>
     <t>type</t>
   </si>
@@ -381,6 +381,15 @@
   </si>
   <si>
     <t>Inicias de Laboratorista</t>
+  </si>
+  <si>
+    <t>fez_ge</t>
+  </si>
+  <si>
+    <t>Fizeram a GE (Gota espessa)?</t>
+  </si>
+  <si>
+    <t>data('fez_ge')==1</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1099,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA48"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.125" style="2" customWidth="1"/>
@@ -1304,26 +1313,45 @@
       <c r="Q9"/>
       <c r="R9"/>
     </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="M10" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="2" t="s">
+      <c r="E12" s="10"/>
+      <c r="F12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M11" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="E12" s="16"/>
     </row>
     <row r="13" spans="1:27" ht="47.25" x14ac:dyDescent="0.25">
       <c r="D13" s="2" t="s">
@@ -1344,27 +1372,21 @@
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D14" s="2" t="s">
-        <v>68</v>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
       </c>
       <c r="E14" s="16"/>
-      <c r="F14" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="10"/>
+        <v>68</v>
+      </c>
+      <c r="E15" s="16"/>
       <c r="F15" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
@@ -1373,56 +1395,58 @@
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D17" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="10"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="D18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="M18" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="M19" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="E20" s="10"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="10"/>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="E21" s="10"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B24" s="10"/>
@@ -1433,7 +1457,6 @@
       <c r="G24" s="10"/>
       <c r="H24" s="15"/>
       <c r="I24" s="10"/>
-      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B25" s="10"/>
@@ -1455,6 +1478,7 @@
       <c r="G26" s="10"/>
       <c r="H26" s="15"/>
       <c r="I26" s="10"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B27" s="10"/>
@@ -1486,31 +1510,31 @@
       <c r="H29" s="15"/>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L32" s="4"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="10"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="10"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="10"/>
+    </row>
+    <row r="31" spans="2:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="L33" s="4"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
       <c r="H40" s="15"/>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
@@ -1520,17 +1544,17 @@
       <c r="H41" s="15"/>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
       <c r="H42" s="15"/>
       <c r="I42" s="10"/>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
@@ -1540,7 +1564,7 @@
       <c r="H43" s="15"/>
       <c r="I43" s="10"/>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
@@ -1550,7 +1574,7 @@
       <c r="H44" s="15"/>
       <c r="I44" s="10"/>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="10"/>
       <c r="C45" s="10"/>
       <c r="D45" s="10"/>
@@ -1560,7 +1584,7 @@
       <c r="H45" s="15"/>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="10"/>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
@@ -1570,7 +1594,7 @@
       <c r="H46" s="15"/>
       <c r="I46" s="10"/>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
@@ -1580,7 +1604,7 @@
       <c r="H47" s="15"/>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B48" s="10"/>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
@@ -1590,15 +1614,25 @@
       <c r="H48" s="15"/>
       <c r="I48" s="10"/>
     </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="10"/>
+    </row>
   </sheetData>
   <autoFilter ref="D1:L1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="6">
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
@@ -2378,6 +2412,14 @@
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>104</v>
@@ -2429,10 +2471,6 @@
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>

--- a/app/config/tables/resultado/forms/resultado/resultado.xlsx
+++ b/app/config/tables/resultado/forms/resultado/resultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celso\odkx\sentinela\app\config\tables\resultado\forms\resultado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50A180A-4271-4CF9-A8ED-0C36C4D34AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EADB469-FAE6-4E24-B2EB-2CCEEF7A59C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-285" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="3" r:id="rId1"/>
@@ -1021,7 +1021,7 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>2022022800</v>
+        <v>2020030801</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
